--- a/public/excel-templates/diagnosis.xlsx
+++ b/public/excel-templates/diagnosis.xlsx
@@ -397,22 +397,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C1"/>
+  <dimension ref="A1:E1"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>Patient ID</v>
+        <v>라벨번호</v>
       </c>
       <c r="B1" t="str">
+        <v>ChiefComplain</v>
+      </c>
+      <c r="C1" t="str">
         <v>Diagnosis</v>
       </c>
-      <c r="C1" t="str">
-        <v>ETC</v>
+      <c r="D1" t="str">
+        <v>TreatmentPlan</v>
+      </c>
+      <c r="E1" t="str">
+        <v>etc</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E1"/>
   </ignoredErrors>
 </worksheet>
 </file>